--- a/KONSPEKT - NAJLEPSZE POLSKIE SOLÓWKI.xlsx
+++ b/KONSPEKT - NAJLEPSZE POLSKIE SOLÓWKI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE SOLÓWKI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E936A8-980E-4E7E-946E-C15C07675919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BADE40C-6EB0-4E72-8AA7-3A5B4A3D3478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26310" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAZA" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="132">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -69,15 +69,9 @@
     <t>TRUDNY</t>
   </si>
   <si>
-    <t>PROSTY</t>
-  </si>
-  <si>
     <t>EXPERT</t>
   </si>
   <si>
-    <t>POCZĄTKUJĄCY</t>
-  </si>
-  <si>
     <t>SOLÓWKA</t>
   </si>
   <si>
@@ -102,21 +96,9 @@
     <t>https://drive.google.com/drive/folders/1gn38kVDNvOW5EzkiJ80A6eFEf-W8-Kbs</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1LU-9x6uD3s1QKan8s1ZFrfDL1M5-rQdY</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1OZgzNrVsmSwdWN_ZSmvcE6-XE8L84RsI</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1tYrsLVTsPdnnDnusJTdb92ygWV4cI16e</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1cf_sTOd-mDAliPeQ5wlcfUtO1W0Lal3B</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1Bhfm2a_iTTjdzzKT3unfS1qtK97mWeQt</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/16J4ItjTKfRccyCli0qCahgxtl9Ew3yEU</t>
   </si>
   <si>
@@ -132,9 +114,6 @@
     <t>https://drive.google.com/drive/folders/1qqlsSt8RT-NjNQd5RgbFKBvWzrf-gDqp</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1TrjdZeETL0525TfS5u5YbqpQVujb_7c4</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1CgrGgXrJrHtyfxzsqWmDICDL8r4RlRSY</t>
   </si>
   <si>
@@ -153,15 +132,9 @@
     <t>https://drive.google.com/drive/folders/1GiKfJWR8nQKfSR1hosz2-_XPaw8JUQTs</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1eLqqUYuA-rbmTiMdCvJ9-9GAacsBBrAs</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1_nt7pnvnQeQ-oHU6OGoG3WLRU15zK5WH</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/0B-ZsE-2yneXrU1hvaHYwR0pTQ2c?resourcekey=0-2tTqQGGV3kbm7FMHZw-GBw</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1SgukbslvLFCd4y7lGh7_64IYwtp6gKMi</t>
   </si>
   <si>
@@ -174,9 +147,6 @@
     <t>https://drive.google.com/drive/folders/1igdheqVTBCUVAAQguJuqD1yNXYszOtg-</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/0B-ZsE-2yneXrNGNGMzE5bFIyTHc?resourcekey=0-ue1dqEWJIZj7wDAdv24PPg</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1j6ZbKjd-r1x8py_UlnDafZetqGzqiJDD</t>
   </si>
   <si>
@@ -189,9 +159,6 @@
     <t>https://drive.google.com/drive/folders/1h5F8TsaH82i0D_QKjBWFTgGTAHUfqw2_</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1kXgv88leXWwkOVjIIqH2kKZIYsQIdkDW</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1dCgTYxbBJpCAAq0Clzl5yCfmeABZjcv5</t>
   </si>
   <si>
@@ -204,15 +171,9 @@
     <t>https://drive.google.com/drive/folders/1mOp5x1SqA_2iHF5kqCifYoJlZpyhwCTk</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/11vgMVnIk-htJwQMd55Qr4j7ADwhcz7oE</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1G1Cbn-Qjy-EZeMv-ZLEcxs0bPGm5T1e0</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/0B-ZsE-2yneXrbVd5TUh5cE9IOWs?resourcekey=0-J8xSFimQdzYeo7OGcLpbhg</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1088vIwnfwUzH2OKo1rpSi_ex2K09xEIi</t>
   </si>
   <si>
@@ -231,27 +192,18 @@
     <t>https://drive.google.com/drive/folders/1xamJt7_Gp0vjg9cqueeHyVrjDSvG0M4w</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1U2nbW8XASib_PrsulQzkwBA0qfEjOLRE</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1harNJAMABLIE8X3uqs6NYVDz4I8M2zSm</t>
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1m-gdNrLpKTyh4MMfRWN8n6_4cpLF7cZZ</t>
   </si>
   <si>
-    <t>Wojciech Gąssowski</t>
-  </si>
-  <si>
     <t>Dżem</t>
   </si>
   <si>
     <t>Happysad</t>
   </si>
   <si>
-    <t>Michael Jackson</t>
-  </si>
-  <si>
     <t>Piraci z Karaibów</t>
   </si>
   <si>
@@ -318,24 +270,12 @@
     <t>Czesław Niemen</t>
   </si>
   <si>
-    <t>Earth Song</t>
-  </si>
-  <si>
-    <t>Enter the Sekai Taikai</t>
-  </si>
-  <si>
     <t>Gdybyś Kochał Hej</t>
   </si>
   <si>
     <t>Piersi</t>
   </si>
   <si>
-    <t>Hallelujah SOLO COVER</t>
-  </si>
-  <si>
-    <t>Id Rather Go Blind</t>
-  </si>
-  <si>
     <t>Jak Malowany Ptak</t>
   </si>
   <si>
@@ -354,15 +294,6 @@
     <t>Patrycja Markowska &amp; Grzegorz Markowski</t>
   </si>
   <si>
-    <t>Lose Control</t>
-  </si>
-  <si>
-    <t>Teddy Swims</t>
-  </si>
-  <si>
-    <t>ZBIGNIEW WODECKI SOLO COVER</t>
-  </si>
-  <si>
     <t>Mała aleja róż</t>
   </si>
   <si>
@@ -381,18 +312,12 @@
     <t>Metallica</t>
   </si>
   <si>
-    <t>Nyan Cat</t>
-  </si>
-  <si>
     <t>Przeżyj to sam</t>
   </si>
   <si>
     <t>Lombard</t>
   </si>
   <si>
-    <t>Przygoda bez miłości - Test</t>
-  </si>
-  <si>
     <t>Ptak i Drzewo</t>
   </si>
   <si>
@@ -405,9 +330,6 @@
     <t>Poluzjanci</t>
   </si>
   <si>
-    <t>Różowa Pantera</t>
-  </si>
-  <si>
     <t>Son Of The Blue Sky</t>
   </si>
   <si>
@@ -420,15 +342,6 @@
     <t>Sztywny Pal Azji</t>
   </si>
   <si>
-    <t>Star Wars Theme SOLO COVER</t>
-  </si>
-  <si>
-    <t>Summer</t>
-  </si>
-  <si>
-    <t>Vivaldi SOLO COVER</t>
-  </si>
-  <si>
     <t>Guns &amp; Roses</t>
   </si>
   <si>
@@ -444,24 +357,9 @@
     <t>Bajm</t>
   </si>
   <si>
-    <t>The Godfather SOLO COVER</t>
-  </si>
-  <si>
-    <t>The Good The Bad And The Ugly</t>
-  </si>
-  <si>
-    <t>The Never Ending Story SOLO COVER</t>
-  </si>
-  <si>
-    <t>The Simpsons Theme</t>
-  </si>
-  <si>
     <t>These Are The Days Of Our Lives</t>
   </si>
   <si>
-    <t>Lari Basilio SOLO COVER</t>
-  </si>
-  <si>
     <t>Too Much Love Will Kill You</t>
   </si>
   <si>
@@ -474,12 +372,6 @@
     <t>Seweryn Krajewski</t>
   </si>
   <si>
-    <t>Wiosna</t>
-  </si>
-  <si>
-    <t>Antonio Vivaldi</t>
-  </si>
-  <si>
     <t>Wokół Sami Lunatycy</t>
   </si>
   <si>
@@ -487,6 +379,48 @@
   </si>
   <si>
     <t>Lady Pank (Live version)</t>
+  </si>
+  <si>
+    <t>SOLO COVER</t>
+  </si>
+  <si>
+    <t>Hans Zimmer</t>
+  </si>
+  <si>
+    <t>Led Zeppelin</t>
+  </si>
+  <si>
+    <t>Lari Basilio</t>
+  </si>
+  <si>
+    <t>Star Wars Theme</t>
+  </si>
+  <si>
+    <t>The Godfather</t>
+  </si>
+  <si>
+    <t>The Never Ending Story</t>
+  </si>
+  <si>
+    <t>Przygoda bez miłości</t>
+  </si>
+  <si>
+    <t>Test, Wojciech Gąssowski</t>
+  </si>
+  <si>
+    <t>John Williams </t>
+  </si>
+  <si>
+    <t>Nino Rota</t>
+  </si>
+  <si>
+    <t>Limahl </t>
+  </si>
+  <si>
+    <t>ŁATWY</t>
+  </si>
+  <si>
+    <t>ZBIGNIEW WODECKI</t>
   </si>
 </sst>
 </file>
@@ -496,7 +430,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -522,6 +456,20 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -550,7 +498,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -560,6 +508,9 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -579,10 +530,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BazaUtworowMaster" displayName="BazaUtworowMaster" ref="A1:K54" totalsRowShown="0">
-  <autoFilter ref="A1:K54" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K54">
-    <sortCondition ref="H1:H54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BazaUtworowMaster" displayName="BazaUtworowMaster" ref="A1:K42" totalsRowShown="0">
+  <autoFilter ref="A1:K42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K42">
+    <sortCondition ref="H1:H42"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR"/>
@@ -796,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -849,1059 +800,842 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="D2" s="6"/>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>69</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="6"/>
       <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="D4" s="6"/>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="D5" s="6"/>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="D6" s="6"/>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="D7" s="6"/>
       <c r="G7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="D8" s="6"/>
       <c r="G8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="D9" s="6"/>
       <c r="G9" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>98</v>
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="D10" s="6"/>
       <c r="G10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D11" s="6"/>
       <c r="G11" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="6">
-        <v>8</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="6"/>
       <c r="G12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>102</v>
+        <v>87</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D13" s="6"/>
       <c r="G13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D14" s="6"/>
       <c r="G14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="6">
+        <v>8</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D16" s="6"/>
       <c r="G16" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K16" s="4"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D17" s="6"/>
       <c r="G17" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D18" s="6"/>
       <c r="G18" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D19" s="6"/>
       <c r="G19" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="6">
-        <v>8</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D20" s="6"/>
       <c r="G20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="6">
+        <v>7</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>118</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D22" s="6"/>
       <c r="G22" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>85</v>
+      <c r="A23" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="D23" s="6"/>
       <c r="G23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D24" s="6"/>
       <c r="G24" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D25" s="6"/>
       <c r="G25" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="6">
-        <v>10</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="6"/>
       <c r="G26" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="6">
-        <v>7</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="6"/>
       <c r="G27" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K27" s="4"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="6">
-        <v>2</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="6"/>
       <c r="G28" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K28" s="4"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" s="6"/>
+      <c r="A29" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="6">
+        <v>6</v>
+      </c>
       <c r="G29" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K29" s="4"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="D30" s="6"/>
       <c r="G30" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K30" s="4"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D31" s="6"/>
       <c r="G31" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K31" s="4"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D32" s="6"/>
       <c r="G32" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K32" s="4"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>126</v>
+      <c r="A33" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K33" s="4"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="6"/>
+      <c r="A34" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="6">
+        <v>7</v>
+      </c>
       <c r="G34" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K34" s="4"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D35" s="6"/>
       <c r="G35" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K35" s="4"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="6">
+        <v>9</v>
+      </c>
       <c r="G36" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K36" s="4"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="6">
-        <v>6</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="6"/>
       <c r="G37" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="6">
-        <v>9</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D38" s="6"/>
       <c r="G38" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="D39" s="6"/>
       <c r="G39" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D40" s="6"/>
       <c r="G40" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D41" s="6"/>
       <c r="G41" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="6">
-        <v>6</v>
-      </c>
+      <c r="A42" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="6"/>
       <c r="G42" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="6">
-        <v>2</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" t="s">
-        <v>17</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K43" s="4"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="6">
-        <v>7</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K44" s="4"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K45" s="4"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="6"/>
-      <c r="G46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="6">
-        <v>9</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K47" s="4"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="G48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H48" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K48" s="4"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="6"/>
-      <c r="G49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H49" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K49" s="4"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D50" s="6"/>
-      <c r="G50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="G51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="6">
-        <v>4</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H52" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K52" s="4"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D53" s="6"/>
-      <c r="G53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="G54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H54" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K54" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1912,56 +1646,44 @@
     <hyperlink ref="J6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
     <hyperlink ref="J7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
     <hyperlink ref="J8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="J9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="J10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="J11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="J14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="J16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="J17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="J18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="J19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="J20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="J21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="J22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="J23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="J24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="J25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="J26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="J27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="J28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="J29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="J30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="J31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="J32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="J33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="J34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="J35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="J36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="J37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="J38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="J39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="J40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="J41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="J42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="J43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="J44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="J45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="J46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="J47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="J48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="J49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="J50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="J51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="J52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="J53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="J54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="J9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="J10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="J11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="J14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="J16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="J18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="J19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="J20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="J21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="J22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="J23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="J24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="J25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="J26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="J27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="J28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="J29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="J30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="J31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="J32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="J33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="J34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="J35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="J36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="J37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="J38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="J39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="J40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="J41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="J42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId54"/>
+    <tablePart r:id="rId42"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NAJLEPSZE POLSKIE SOLÓWKI.xlsx
+++ b/KONSPEKT - NAJLEPSZE POLSKIE SOLÓWKI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE SOLÓWKI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E44A17E-BB2B-4298-BAA6-8A452498A4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D1F38A-2D11-4A46-8694-729239383FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26310" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAZA" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -80,9 +80,6 @@
     <t>SOLÓWKA</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1pvUo-r0pwCKpVltTJvPfqddttpSlKYVb</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1JNVw4CSlTcnd_z5uk_o5Iza9c1d3tV5d</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>Dżem</t>
   </si>
   <si>
-    <t>Happysad</t>
-  </si>
-  <si>
     <t>Lady Pank</t>
   </si>
   <si>
@@ -191,9 +185,6 @@
     <t>Wehikuł Czasu</t>
   </si>
   <si>
-    <t>30 Raz</t>
-  </si>
-  <si>
     <t>Adres w Sercu</t>
   </si>
   <si>
@@ -233,9 +224,6 @@
     <t>Kołysanka</t>
   </si>
   <si>
-    <t>Patrycja Markowska &amp; Grzegorz Markowski</t>
-  </si>
-  <si>
     <t>Mała aleja róż</t>
   </si>
   <si>
@@ -314,13 +302,16 @@
     <t>Test, Wojciech Gąssowski</t>
   </si>
   <si>
-    <t>ŁATWY</t>
-  </si>
-  <si>
     <t>Zbigniew Wodecki</t>
   </si>
   <si>
     <t>Zawsze tam gdzie Ty (Arr. Mariusz Tryba)</t>
+  </si>
+  <si>
+    <t>Patrycja &amp; Grzegorz Markowscy</t>
+  </si>
+  <si>
+    <t>PROSTY</t>
   </si>
 </sst>
 </file>
@@ -341,21 +332,29 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
@@ -427,10 +426,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BazaUtworowMaster" displayName="BazaUtworowMaster" ref="A1:J30" totalsRowShown="0">
-  <autoFilter ref="A1:J30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J30">
-    <sortCondition ref="G1:G30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BazaUtworowMaster" displayName="BazaUtworowMaster" ref="A1:J29" totalsRowShown="0">
+  <autoFilter ref="A1:J29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J29">
+    <sortCondition ref="G1:G29"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="UTWÓR"/>
@@ -643,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -692,13 +691,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
@@ -713,13 +712,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>13</v>
@@ -734,10 +733,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>10</v>
@@ -755,13 +754,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -776,10 +775,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>11</v>
@@ -788,7 +787,7 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
@@ -797,19 +796,19 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C7" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>19</v>
@@ -818,13 +817,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -839,13 +838,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>11</v>
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -860,13 +859,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -881,13 +880,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -902,10 +901,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -923,13 +922,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -944,12 +943,12 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -965,13 +964,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -986,10 +985,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -1007,10 +1006,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -1028,10 +1027,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -1048,11 +1047,11 @@
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>72</v>
+      <c r="A19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -1069,11 +1068,11 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>91</v>
+      <c r="A20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -1091,13 +1090,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>13</v>
@@ -1112,13 +1111,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>13</v>
@@ -1133,10 +1132,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -1154,13 +1153,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>13</v>
@@ -1175,13 +1174,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>13</v>
@@ -1196,10 +1195,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1217,10 +1216,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1238,13 +1237,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>13</v>
@@ -1258,14 +1257,14 @@
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>87</v>
+      <c r="A29" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>13</v>
@@ -1278,68 +1277,46 @@
       </c>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F42" t="str">
+    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F41" t="str">
         <f>PROPER(B1)</f>
         <v>Wykonawca</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="I20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="I21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="I23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="I24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="I25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="I26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="I27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="I28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="I29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="I30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="I20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="I21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="I23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="I24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="I25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="I26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="I27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="I28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="I29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId29"/>
   </tableParts>
 </worksheet>
 </file>
--- a/KONSPEKT - NAJLEPSZE POLSKIE SOLÓWKI.xlsx
+++ b/KONSPEKT - NAJLEPSZE POLSKIE SOLÓWKI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\[PATRONITE] - MATERIAŁY WORD I PDF\HTML - NAJLEPSZE POLSKIE SOLÓWKI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D1F38A-2D11-4A46-8694-729239383FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AA95F3-5F31-4C52-9ACF-6E0E84FB6146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18990" yWindow="-105" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAZA" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="95">
   <si>
     <t>UTWÓR</t>
   </si>
@@ -312,6 +312,15 @@
   </si>
   <si>
     <t>PROSTY</t>
+  </si>
+  <si>
+    <t>Kocham wolność</t>
+  </si>
+  <si>
+    <t>Chłopcy z Placu Broni</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1rMG29rILTaR5sAJILQJQlxl9mFcxPbcx&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -321,7 +330,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -370,6 +379,12 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -393,11 +408,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -407,8 +423,11 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperłącze" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -426,8 +445,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BazaUtworowMaster" displayName="BazaUtworowMaster" ref="A1:J29" totalsRowShown="0">
-  <autoFilter ref="A1:J29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BazaUtworowMaster" displayName="BazaUtworowMaster" ref="A1:J30" totalsRowShown="0">
+  <autoFilter ref="A1:J30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J29">
     <sortCondition ref="G1:G29"/>
   </sortState>
@@ -1277,6 +1296,29 @@
       </c>
       <c r="J29" s="4"/>
     </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J30" s="9">
+        <v>46255</v>
+      </c>
+    </row>
     <row r="41" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F41" t="str">
         <f>PROPER(B1)</f>
@@ -1313,10 +1355,11 @@
     <hyperlink ref="I27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
     <hyperlink ref="I28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
     <hyperlink ref="I29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="I30" r:id="rId29" xr:uid="{7683A798-9853-4650-987B-51FCB532175C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId29"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>